--- a/TestData/LV_TMTT0022031_VerifyFunctionalityAddNewActivitiesAndVerifyTheSameOnMyActivityDashboard.xlsx
+++ b/TestData/LV_TMTT0022031_VerifyFunctionalityAddNewActivitiesAndVerifyTheSameOnMyActivityDashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EBB983-5AE2-42F8-8316-7C1E9FD34417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF77A17-92DF-4356-8268-DB42A9B709FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>Users</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>CF Financial User</t>
+  </si>
+  <si>
+    <t>AppName</t>
   </si>
 </sst>
 </file>
@@ -716,10 +719,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D94281-534A-422C-BC54-5423A93D66A9}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
